--- a/results/0916-all/松嫩－三江平原农业区/tech_selected_summary.xlsx
+++ b/results/0916-all/松嫩－三江平原农业区/tech_selected_summary.xlsx
@@ -337,163 +337,163 @@
     <t>中新食品区</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -502,7 +502,7 @@
     <t>EEF(NI)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 4045068.86</t>
+    <t>4045068.86</t>
   </si>
   <si>
     <t>Increasing byproduct_pig</t>
@@ -643,10 +643,10 @@
     <t>4R(Right rate)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 1255591702.08</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>1255591702.08</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Physical additives_pig</t>
@@ -661,34 +661,34 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 382802333.36</t>
-  </si>
-  <si>
-    <t>总经济成本: 17638666.59</t>
+    <t>382802333.36</t>
+  </si>
+  <si>
+    <t>17638666.59</t>
   </si>
   <si>
     <t>cover crop (non-leguminous)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 4715533.09</t>
-  </si>
-  <si>
-    <t>总经济成本: 62105716.01</t>
+    <t>4715533.09</t>
+  </si>
+  <si>
+    <t>62105716.01</t>
   </si>
   <si>
     <t>Oil_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 283764992.97</t>
-  </si>
-  <si>
-    <t>总经济成本: 2781013.50</t>
+    <t>283764992.97</t>
+  </si>
+  <si>
+    <t>2781013.50</t>
   </si>
   <si>
     <t>4R(Right time)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 36178412.60</t>
+    <t>36178412.60</t>
   </si>
   <si>
     <t>Yucca extract_Poultry</t>
@@ -715,10 +715,10 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 73505754.49</t>
-  </si>
-  <si>
-    <t>总经济成本: 9253505.55</t>
+    <t>73505754.49</t>
+  </si>
+  <si>
+    <t>9253505.55</t>
   </si>
   <si>
     <t>Biochar_sheep &amp; goat</t>
@@ -727,7 +727,7 @@
     <t>4R(Right type)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 71145440.75</t>
+    <t>71145440.75</t>
   </si>
   <si>
     <t>Probiotics_poultry</t>
@@ -745,16 +745,16 @@
     <t>EEF(CRF)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 146113357.19</t>
-  </si>
-  <si>
-    <t>总经济成本: 212538146.36</t>
-  </si>
-  <si>
-    <t>总经济成本: 47418.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 517622.23</t>
+    <t>146113357.19</t>
+  </si>
+  <si>
+    <t>212538146.36</t>
+  </si>
+  <si>
+    <t>47418.00</t>
+  </si>
+  <si>
+    <t>517622.23</t>
   </si>
   <si>
     <t>nitrification inhibitor_sheep&amp;goat</t>
@@ -763,19 +763,19 @@
     <t>incorporation_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 329222856.85</t>
-  </si>
-  <si>
-    <t>总经济成本: 14887589.45</t>
+    <t>329222856.85</t>
+  </si>
+  <si>
+    <t>14887589.45</t>
   </si>
   <si>
     <t>Adsorbent_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 73979.17</t>
-  </si>
-  <si>
-    <t>总经济成本: 1040247.00</t>
+    <t>73979.17</t>
+  </si>
+  <si>
+    <t>1040247.00</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
@@ -787,115 +787,115 @@
     <t>EEF(NI)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 155296971.94</t>
-  </si>
-  <si>
-    <t>总经济成本: 5153819.00</t>
+    <t>155296971.94</t>
+  </si>
+  <si>
+    <t>5153819.00</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 542999917.23</t>
+    <t>542999917.23</t>
   </si>
   <si>
     <t>Plant-derived N substitution_maize</t>
   </si>
   <si>
-    <t>总经济成本: 780484858.18</t>
-  </si>
-  <si>
-    <t>总经济成本: 123217920.23</t>
-  </si>
-  <si>
-    <t>总经济成本: 529386.32</t>
+    <t>780484858.18</t>
+  </si>
+  <si>
+    <t>123217920.23</t>
+  </si>
+  <si>
+    <t>529386.32</t>
   </si>
   <si>
     <t>compost（low）≤30%_maize</t>
   </si>
   <si>
-    <t>总经济成本: 545714351.98</t>
-  </si>
-  <si>
-    <t>总经济成本: 190326799.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 9900929.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 166024766.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 191206.02</t>
-  </si>
-  <si>
-    <t>总经济成本: 482245.28</t>
-  </si>
-  <si>
-    <t>总经济成本: 179244857.96</t>
+    <t>545714351.98</t>
+  </si>
+  <si>
+    <t>190326799.89</t>
+  </si>
+  <si>
+    <t>9900929.20</t>
+  </si>
+  <si>
+    <t>166024766.91</t>
+  </si>
+  <si>
+    <t>191206.02</t>
+  </si>
+  <si>
+    <t>482245.28</t>
+  </si>
+  <si>
+    <t>179244857.96</t>
   </si>
   <si>
     <t>4R(Right place)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 406931305.21</t>
-  </si>
-  <si>
-    <t>总经济成本: 149459561.71</t>
-  </si>
-  <si>
-    <t>总经济成本: 414840385.04</t>
-  </si>
-  <si>
-    <t>总经济成本: 23933143.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 92739030.70</t>
-  </si>
-  <si>
-    <t>总经济成本: 33006842.31</t>
-  </si>
-  <si>
-    <t>总经济成本: 4431539.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 526277.88</t>
+    <t>406931305.21</t>
+  </si>
+  <si>
+    <t>149459561.71</t>
+  </si>
+  <si>
+    <t>414840385.04</t>
+  </si>
+  <si>
+    <t>23933143.03</t>
+  </si>
+  <si>
+    <t>92739030.70</t>
+  </si>
+  <si>
+    <t>33006842.31</t>
+  </si>
+  <si>
+    <t>4431539.00</t>
+  </si>
+  <si>
+    <t>526277.88</t>
   </si>
   <si>
     <t>Increasing concentrate level (grain)_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 66969720.00</t>
+    <t>66969720.00</t>
   </si>
   <si>
     <t>cover crop (mix)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 53458678.44</t>
-  </si>
-  <si>
-    <t>总经济成本: 11677390.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 1037468030.46</t>
-  </si>
-  <si>
-    <t>总经济成本: 18745160.48</t>
-  </si>
-  <si>
-    <t>总经济成本: 13059715.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 40670703.74</t>
-  </si>
-  <si>
-    <t>总经济成本: 3059.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 329940.80</t>
-  </si>
-  <si>
-    <t>总经济成本: 11991581.99</t>
+    <t>53458678.44</t>
+  </si>
+  <si>
+    <t>11677390.89</t>
+  </si>
+  <si>
+    <t>1037468030.46</t>
+  </si>
+  <si>
+    <t>18745160.48</t>
+  </si>
+  <si>
+    <t>13059715.50</t>
+  </si>
+  <si>
+    <t>40670703.74</t>
+  </si>
+  <si>
+    <t>3059.20</t>
+  </si>
+  <si>
+    <t>329940.80</t>
+  </si>
+  <si>
+    <t>11991581.99</t>
   </si>
   <si>
     <t>EEF(NI)_friut</t>
@@ -907,40 +907,40 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 995798146.04</t>
-  </si>
-  <si>
-    <t>总经济成本: 212566791.46</t>
-  </si>
-  <si>
-    <t>总经济成本: 46031701.61</t>
-  </si>
-  <si>
-    <t>总经济成本: 1748.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 4523112.16</t>
-  </si>
-  <si>
-    <t>总经济成本: 224858449.07</t>
-  </si>
-  <si>
-    <t>总经济成本: 7574540.29</t>
-  </si>
-  <si>
-    <t>总经济成本: 6264043.21</t>
-  </si>
-  <si>
-    <t>总经济成本: 2715047.31</t>
-  </si>
-  <si>
-    <t>总经济成本: 17690291.37</t>
-  </si>
-  <si>
-    <t>总经济成本: 18774163.41</t>
-  </si>
-  <si>
-    <t>总经济成本: 145687923.91</t>
+    <t>995798146.04</t>
+  </si>
+  <si>
+    <t>212566791.46</t>
+  </si>
+  <si>
+    <t>46031701.61</t>
+  </si>
+  <si>
+    <t>1748.00</t>
+  </si>
+  <si>
+    <t>4523112.16</t>
+  </si>
+  <si>
+    <t>224858449.07</t>
+  </si>
+  <si>
+    <t>7574540.29</t>
+  </si>
+  <si>
+    <t>6264043.21</t>
+  </si>
+  <si>
+    <t>2715047.31</t>
+  </si>
+  <si>
+    <t>17690291.37</t>
+  </si>
+  <si>
+    <t>18774163.41</t>
+  </si>
+  <si>
+    <t>145687923.91</t>
   </si>
   <si>
     <t>Low protein diet_Pig</t>
@@ -997,7 +997,7 @@
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 1139543853.59</t>
+    <t>1139543853.59</t>
   </si>
   <si>
     <t>Nitrocompounds_beef cattle</t>
@@ -1009,28 +1009,28 @@
     <t>Screw press_pig</t>
   </si>
   <si>
-    <t>总经济成本: 885319232.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 76110.14</t>
-  </si>
-  <si>
-    <t>总经济成本: 160601913.08</t>
-  </si>
-  <si>
-    <t>总经济成本: 235648014.63</t>
-  </si>
-  <si>
-    <t>总经济成本: 8046624.02</t>
+    <t>885319232.00</t>
+  </si>
+  <si>
+    <t>76110.14</t>
+  </si>
+  <si>
+    <t>160601913.08</t>
+  </si>
+  <si>
+    <t>235648014.63</t>
+  </si>
+  <si>
+    <t>8046624.02</t>
   </si>
   <si>
     <t>Zeolite_pig</t>
   </si>
   <si>
-    <t>总经济成本: 1803471.04</t>
-  </si>
-  <si>
-    <t>总经济成本: 4549098.80</t>
+    <t>1803471.04</t>
+  </si>
+  <si>
+    <t>4549098.80</t>
   </si>
   <si>
     <t>Cover_poultry</t>
@@ -1048,28 +1048,28 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 961631618.32</t>
-  </si>
-  <si>
-    <t>总经济成本: 311176362.48</t>
-  </si>
-  <si>
-    <t>总经济成本: 145923994.29</t>
-  </si>
-  <si>
-    <t>总经济成本: 570748712.97</t>
-  </si>
-  <si>
-    <t>总经济成本: 617906996.90</t>
-  </si>
-  <si>
-    <t>总经济成本: 87414210.58</t>
-  </si>
-  <si>
-    <t>总经济成本: 531719816.49</t>
-  </si>
-  <si>
-    <t>总经济成本: 170474.96</t>
+    <t>961631618.32</t>
+  </si>
+  <si>
+    <t>311176362.48</t>
+  </si>
+  <si>
+    <t>145923994.29</t>
+  </si>
+  <si>
+    <t>570748712.97</t>
+  </si>
+  <si>
+    <t>617906996.90</t>
+  </si>
+  <si>
+    <t>87414210.58</t>
+  </si>
+  <si>
+    <t>531719816.49</t>
+  </si>
+  <si>
+    <t>170474.96</t>
   </si>
 </sst>
 </file>
